--- a/Data/GP2_FCR_wk.xlsx
+++ b/Data/GP2_FCR_wk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Guinea-Pig-data_2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88652D9-ABD7-4FDC-A21A-C12B6F24B5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF47F270-B2E7-4A67-B458-F7D225EAAAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{734AADDA-D696-41A3-9F06-4D2A029AA065}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{734AADDA-D696-41A3-9F06-4D2A029AA065}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -131,12 +131,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -474,33 +468,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38282449-6950-46A6-991B-F7BD99BB971E}">
   <dimension ref="A1:F81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="9.140625" style="1"/>
+    <col min="1" max="3" width="9.1796875" style="1"/>
     <col min="4" max="5" width="12" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -521,7 +515,7 @@
         <v>2.9095563139931748</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -542,7 +536,7 @@
         <v>3.995348837209304</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -563,7 +557,7 @@
         <v>5.1304347826087024</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -584,7 +578,7 @@
         <v>5.0062500000000041</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -605,7 +599,7 @@
         <v>4.1160377358490567</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -626,7 +620,7 @@
         <v>6.0642585129589337</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -646,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -667,7 +661,7 @@
         <v>20.149333333333395</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -688,7 +682,7 @@
         <v>13.797849462365617</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -709,7 +703,7 @@
         <v>10.716546762589958</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -730,7 +724,7 @@
         <v>4.2580645161290365</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -751,7 +745,7 @@
         <v>27.492063492063487</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -772,7 +766,7 @@
         <v>7.2947761194030019</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -793,7 +787,7 @@
         <v>6.9265734265734364</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -813,7 +807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -834,7 +828,7 @@
         <v>6.0865051903114313</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -847,14 +841,14 @@
       <c r="D18" s="1">
         <v>28.11428571428571</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -870,11 +864,11 @@
       <c r="E19" s="1">
         <v>0.24285714285714199</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
@@ -895,7 +889,7 @@
         <v>8.0407331975560243</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
@@ -916,7 +910,7 @@
         <v>8.3258655804480828</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -937,7 +931,7 @@
         <v>3.3023715415019801</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -958,7 +952,7 @@
         <v>7.6857142857142868</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -971,14 +965,14 @@
       <c r="D24" s="1">
         <v>27.517857142857139</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,7 +993,7 @@
         <v>3.6122047244094531</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -1020,7 +1014,7 @@
         <v>5.8923841059602715</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,7 +1035,7 @@
         <v>8.4716981132075713</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
@@ -1054,14 +1048,14 @@
       <c r="D28" s="1">
         <v>25.88571428571429</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -1077,11 +1071,11 @@
       <c r="E29" s="1">
         <v>0.3</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F29" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -1102,7 +1096,7 @@
         <v>8.7311827956989294</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,7 +1117,7 @@
         <v>8.1290322580645196</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>7</v>
       </c>
@@ -1144,7 +1138,7 @@
         <v>3.0229508196721326</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>7</v>
       </c>
@@ -1165,7 +1159,7 @@
         <v>3.8755555555555596</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>7</v>
       </c>
@@ -1186,7 +1180,7 @@
         <v>5.5354231974921673</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,7 +1201,7 @@
         <v>3.693959731543627</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>7</v>
       </c>
@@ -1228,7 +1222,7 @@
         <v>6.3519650655021875</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>7</v>
       </c>
@@ -1249,7 +1243,7 @@
         <v>3.8684210526315788</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -1269,7 +1263,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,7 +1284,7 @@
         <v>15.077528089887682</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
@@ -1311,7 +1305,7 @@
         <v>6.8847058823529439</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -1332,7 +1326,7 @@
         <v>6.9176470588235315</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>8</v>
       </c>
@@ -1353,7 +1347,7 @@
         <v>4.2533132530120472</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>8</v>
       </c>
@@ -1374,7 +1368,7 @@
         <v>6.4484631147541043</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>8</v>
       </c>
@@ -1395,7 +1389,7 @@
         <v>9.0094339622641506</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>8</v>
       </c>
@@ -1408,14 +1402,14 @@
       <c r="D45" s="1">
         <v>25.657142857142858</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>8</v>
       </c>
@@ -1436,7 +1430,7 @@
         <v>6.4909420289855113</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>8</v>
       </c>
@@ -1457,7 +1451,7 @@
         <v>5.232671480144413</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>8</v>
       </c>
@@ -1470,14 +1464,14 @@
       <c r="D48" s="1">
         <v>22.574999999999999</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>8</v>
       </c>
@@ -1490,14 +1484,14 @@
       <c r="D49" s="1">
         <v>21.93214285714286</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>8</v>
       </c>
@@ -1518,7 +1512,7 @@
         <v>8.8902439024390496</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>8</v>
       </c>
@@ -1539,7 +1533,7 @@
         <v>10.064634146341493</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>8</v>
       </c>
@@ -1560,7 +1554,7 @@
         <v>3.9272349272349274</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>8</v>
       </c>
@@ -1581,7 +1575,7 @@
         <v>7.2798507462686732</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>8</v>
       </c>
@@ -1602,7 +1596,7 @@
         <v>15.597321428571499</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>8</v>
       </c>
@@ -1623,7 +1617,7 @@
         <v>5.625000000000008</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>8</v>
       </c>
@@ -1644,7 +1638,7 @@
         <v>8.1726457399103136</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>8</v>
       </c>
@@ -1665,7 +1659,7 @@
         <v>12.891366906474858</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>8</v>
       </c>
@@ -1678,14 +1672,14 @@
       <c r="D58" s="1">
         <v>28.5</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>8</v>
       </c>
@@ -1701,11 +1695,11 @@
       <c r="E59" s="1">
         <v>1.07936507936507</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F59" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>8</v>
       </c>
@@ -1726,7 +1720,7 @@
         <v>11.876470588235335</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>8</v>
       </c>
@@ -1747,7 +1741,7 @@
         <v>12.352941176470631</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>9</v>
       </c>
@@ -1768,7 +1762,7 @@
         <v>3.562790697674421</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>9</v>
       </c>
@@ -1789,7 +1783,7 @@
         <v>4.8386167146974124</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>9</v>
       </c>
@@ -1810,7 +1804,7 @@
         <v>8.07456140350879</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>9</v>
       </c>
@@ -1831,7 +1825,7 @@
         <v>3.9467849223946803</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>9</v>
       </c>
@@ -1852,7 +1846,7 @@
         <v>6.6642066420664232</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>9</v>
       </c>
@@ -1873,7 +1867,7 @@
         <v>4.7479452054794562</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>9</v>
       </c>
@@ -1886,14 +1880,14 @@
       <c r="D68" s="1">
         <v>25.267857142857139</v>
       </c>
-      <c r="E68" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E68" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>9</v>
       </c>
@@ -1906,14 +1900,14 @@
       <c r="D69" s="1">
         <v>26.285714285714281</v>
       </c>
-      <c r="E69" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>9</v>
       </c>
@@ -1934,7 +1928,7 @@
         <v>7.6041450777202115</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>9</v>
       </c>
@@ -1955,7 +1949,7 @@
         <v>8.3129533678756502</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>9</v>
       </c>
@@ -1976,7 +1970,7 @@
         <v>3.4261036468330146</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>9</v>
       </c>
@@ -1997,7 +1991,7 @@
         <v>5.8947368421052682</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>9</v>
       </c>
@@ -2018,7 +2012,7 @@
         <v>8.4700854700854755</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>9</v>
       </c>
@@ -2039,7 +2033,7 @@
         <v>5.8314285714285718</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>9</v>
       </c>
@@ -2060,7 +2054,7 @@
         <v>5.7327823691460127</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>9</v>
       </c>
@@ -2081,7 +2075,7 @@
         <v>8.412500000000021</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>9</v>
       </c>
@@ -2101,7 +2095,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>9</v>
       </c>
@@ -2114,14 +2108,14 @@
       <c r="D79" s="1">
         <v>27.87142857142857</v>
       </c>
-      <c r="E79" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>9</v>
       </c>
@@ -2142,7 +2136,7 @@
         <v>8.9565217391304515</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>9</v>
       </c>
